--- a/mis-portal/reports/2026-06-08/IWS_Fincorp_20260608.xlsx
+++ b/mis-portal/reports/2026-06-08/IWS_Fincorp_20260608.xlsx
@@ -18,8 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="5">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="DD-MMM-YYYY"/>
+    <numFmt numFmtId="165" formatCode="₹#,##0.00"/>
+  </numFmts>
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -47,12 +50,16 @@
     </font>
     <font>
       <name val="Calibri"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
       <i val="1"/>
       <color rgb="00595959"/>
       <sz val="8"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -72,6 +79,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00D6E4F0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
     <fill>
@@ -111,7 +123,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -122,11 +134,29 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="10" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -492,7 +522,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M20"/>
+  <dimension ref="A1:M23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -598,134 +628,211 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+    <row r="4" ht="16" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>MF — Debt / Liquid Funds</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>DSP Corporate Bond Fund - Reg - Growth</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n"/>
+      <c r="C5" s="6" t="n">
+        <v>997421.23</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>1242848.78</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>1242848.7819</v>
+      </c>
+      <c r="F5" s="6" t="n"/>
+      <c r="G5" s="6" t="n"/>
+      <c r="H5" s="6" t="n"/>
+      <c r="I5" s="6" t="n">
+        <v>245427.55</v>
+      </c>
+      <c r="J5" s="7" t="n"/>
+      <c r="K5" s="7" t="n">
+        <v>0.246062</v>
+      </c>
+      <c r="L5" s="7" t="n"/>
+      <c r="M5" s="8" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>Total MF Debt / Liquid</t>
+        </is>
+      </c>
+      <c r="C6" s="10">
+        <f>SUM(C5:C5)</f>
+        <v/>
+      </c>
+      <c r="D6" s="10">
+        <f>SUM(D5:D5)</f>
+        <v/>
+      </c>
+      <c r="E6" s="10">
+        <f>SUM(E5:E5)</f>
+        <v/>
+      </c>
+      <c r="F6" s="10">
+        <f>SUM(F5:F5)</f>
+        <v/>
+      </c>
+      <c r="G6" s="10">
+        <f>SUM(G5:G5)</f>
+        <v/>
+      </c>
+      <c r="H6" s="10">
+        <f>SUM(H5:H5)</f>
+        <v/>
+      </c>
+      <c r="I6" s="10">
+        <f>SUM(I5:I5)</f>
+        <v/>
+      </c>
+      <c r="J6" s="11" t="n"/>
+      <c r="K6" s="11" t="n"/>
+      <c r="L6" s="11" t="n"/>
+      <c r="M6" s="11" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>A. TOTAL FIXED INCOME</t>
         </is>
       </c>
-      <c r="C4" s="5" t="n"/>
-      <c r="D4" s="5" t="n"/>
-      <c r="E4" s="5" t="n"/>
-      <c r="F4" s="5" t="n"/>
-      <c r="G4" s="5" t="n"/>
-      <c r="H4" s="5" t="n"/>
-      <c r="I4" s="5" t="n"/>
-      <c r="J4" s="5" t="n"/>
-      <c r="K4" s="5" t="n"/>
-      <c r="L4" s="5" t="n"/>
-      <c r="M4" s="5" t="n"/>
-    </row>
-    <row r="6" ht="16" customHeight="1">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>EQUITY</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>B. TOTAL EQUITY</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="n"/>
-      <c r="D7" s="5" t="n"/>
-      <c r="E7" s="5" t="n"/>
-      <c r="F7" s="5" t="n"/>
-      <c r="G7" s="5" t="n"/>
-      <c r="H7" s="5" t="n"/>
-      <c r="I7" s="5" t="n"/>
-      <c r="J7" s="5" t="n"/>
-      <c r="K7" s="5" t="n"/>
-      <c r="L7" s="5" t="n"/>
-      <c r="M7" s="5" t="n"/>
+      <c r="C7" s="11" t="n"/>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="11" t="n"/>
+      <c r="H7" s="11" t="n"/>
+      <c r="I7" s="11" t="n"/>
+      <c r="J7" s="11" t="n"/>
+      <c r="K7" s="11" t="n"/>
+      <c r="L7" s="11" t="n"/>
+      <c r="M7" s="11" t="n"/>
     </row>
     <row r="9" ht="16" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>ALTERNATES</t>
+          <t>EQUITY</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>D. TOTAL ALTERNATES</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="n"/>
-      <c r="D10" s="5" t="n"/>
-      <c r="E10" s="5" t="n"/>
-      <c r="F10" s="5" t="n"/>
-      <c r="G10" s="5" t="n"/>
-      <c r="H10" s="5" t="n"/>
-      <c r="I10" s="5" t="n"/>
-      <c r="J10" s="5" t="n"/>
-      <c r="K10" s="5" t="n"/>
-      <c r="L10" s="5" t="n"/>
-      <c r="M10" s="5" t="n"/>
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>B. TOTAL EQUITY</t>
+        </is>
+      </c>
+      <c r="C10" s="11" t="n"/>
+      <c r="D10" s="11" t="n"/>
+      <c r="E10" s="11" t="n"/>
+      <c r="F10" s="11" t="n"/>
+      <c r="G10" s="11" t="n"/>
+      <c r="H10" s="11" t="n"/>
+      <c r="I10" s="11" t="n"/>
+      <c r="J10" s="11" t="n"/>
+      <c r="K10" s="11" t="n"/>
+      <c r="L10" s="11" t="n"/>
+      <c r="M10" s="11" t="n"/>
     </row>
     <row r="12" ht="16" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
+          <t>ALTERNATES</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>D. TOTAL ALTERNATES</t>
+        </is>
+      </c>
+      <c r="C13" s="11" t="n"/>
+      <c r="D13" s="11" t="n"/>
+      <c r="E13" s="11" t="n"/>
+      <c r="F13" s="11" t="n"/>
+      <c r="G13" s="11" t="n"/>
+      <c r="H13" s="11" t="n"/>
+      <c r="I13" s="11" t="n"/>
+      <c r="J13" s="11" t="n"/>
+      <c r="K13" s="11" t="n"/>
+      <c r="L13" s="11" t="n"/>
+      <c r="M13" s="11" t="n"/>
+    </row>
+    <row r="15" ht="16" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
           <t>E. Funds in Transit</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="16" customHeight="1">
-      <c r="A14" s="3" t="inlineStr">
+    <row r="17" ht="16" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>F. Broker Balance</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="16" customHeight="1">
-      <c r="A16" s="3" t="inlineStr">
+    <row r="19" ht="16" customHeight="1">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>G. Funds in Bank</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="9" t="inlineStr">
         <is>
           <t>H. GRAND TOTAL (A+B+D+E+F+G)</t>
         </is>
       </c>
-      <c r="C18" s="5" t="n"/>
-      <c r="D18" s="5" t="n"/>
-      <c r="E18" s="5" t="n"/>
-      <c r="F18" s="5" t="n"/>
-      <c r="G18" s="5" t="n"/>
-      <c r="H18" s="5" t="n"/>
-      <c r="I18" s="5" t="n"/>
-      <c r="J18" s="5" t="n"/>
-      <c r="K18" s="5" t="n"/>
-      <c r="L18" s="5" t="n"/>
-      <c r="M18" s="5" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="6" t="inlineStr">
-        <is>
-          <t>Report generated on 08 Jun 2026 10:06 UTC  |  MF data auto-populated from CAS  |  Manual inputs as last updated in portal</t>
+      <c r="C21" s="11" t="n"/>
+      <c r="D21" s="11" t="n"/>
+      <c r="E21" s="11" t="n"/>
+      <c r="F21" s="11" t="n"/>
+      <c r="G21" s="11" t="n"/>
+      <c r="H21" s="11" t="n"/>
+      <c r="I21" s="11" t="n"/>
+      <c r="J21" s="11" t="n"/>
+      <c r="K21" s="11" t="n"/>
+      <c r="L21" s="11" t="n"/>
+      <c r="M21" s="11" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="12" t="inlineStr">
+        <is>
+          <t>Report generated on 08 Jun 2026 11:25 UTC  |  MF data auto-populated from CAS  |  Manual inputs as last updated in portal</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="12">
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A14:M14"/>
+  <mergeCells count="14">
+    <mergeCell ref="A19:M19"/>
+    <mergeCell ref="A21:B21"/>
     <mergeCell ref="A1:M1"/>
     <mergeCell ref="A7:B7"/>
-    <mergeCell ref="A6:M6"/>
+    <mergeCell ref="A23:M23"/>
     <mergeCell ref="A10:B10"/>
     <mergeCell ref="A9:M9"/>
+    <mergeCell ref="A4:M4"/>
     <mergeCell ref="A12:M12"/>
     <mergeCell ref="A3:M3"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="A20:M20"/>
-    <mergeCell ref="A16:M16"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A17:M17"/>
+    <mergeCell ref="A15:M15"/>
+    <mergeCell ref="A6:B6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
